--- a/GOOS_EOV_Species_List.xlsx
+++ b/GOOS_EOV_Species_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jebyrnes/Library/CloudStorage/GoogleDrive-jarrett.byrnes@gmail.com/.shortcut-targets-by-id/1uNfJ83WmlmCErHo4iUjWr1UYx8ZEmsih/Macroalgal EOV Data Processing docs/SOP_Visual/data_entry_forms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jebyrnes/Library/CloudStorage/GoogleDrive-jarrett.byrnes@gmail.com/.shortcut-targets-by-id/1uNfJ83WmlmCErHo4iUjWr1UYx8ZEmsih/Macroalgal EOV Data Processing docs/SOP_Visual/goos_data_sheets_and_entry_forms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{924342DD-8151-5C4C-9BCA-916D37A180E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6869AF6-076D-6446-A517-06FDC5553227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="2700" windowWidth="26040" windowHeight="14940" xr2:uid="{E73D891F-292C-0E46-821D-1D7DB743B82F}"/>
+    <workbookView xWindow="4020" yWindow="2700" windowWidth="26040" windowHeight="14940" activeTab="1" xr2:uid="{E73D891F-292C-0E46-821D-1D7DB743B82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>Variable Name</t>
   </si>
@@ -109,22 +109,23 @@
   </si>
   <si>
     <t>The code for an individual entity sampled in the field.</t>
+  </si>
+  <si>
+    <t>Essential Ocean Variable</t>
+  </si>
+  <si>
+    <t>The name of the GOOS Essential Ocean Variable (see https://goosocean.org/what-we-do/framework/essential-ocean-variables/) that this species falls under. For example, Marine Macroalgal Canopy Cover and Composition. Species not in the macroalgal EOV might be recorded by a sampling schema, and this will enable later sorting of data sets for EOV product documentation. See the EOV specification  sheets for more information.  If the species is not part of an EOV, leave blank.</t>
+  </si>
+  <si>
+    <t>GOOS EOV List</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -146,7 +147,8 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="13"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -172,12 +174,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -196,9 +206,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -236,7 +246,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -342,7 +352,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,7 +494,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -492,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94DDDE4-7A53-3046-AD9E-6CA9BA9C81F9}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
@@ -502,33 +512,37 @@
     <col min="5" max="5" width="31.6640625" customWidth="1"/>
     <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.6640625" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -538,21 +552,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAAA031-AF7F-BC4F-A79B-CBCE2ADDC482}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -565,11 +579,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -578,11 +592,11 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -593,11 +607,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -608,11 +622,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -621,11 +635,11 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -634,11 +648,11 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -649,11 +663,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -668,13 +682,27 @@
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="4"/>
       <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="162" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
